--- a/BOM/PCB_BOM.xlsx
+++ b/BOM/PCB_BOM.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12300"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Power_bank_PCB" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="122">
   <si>
     <t>Reference,</t>
   </si>
@@ -41,7 +41,10 @@
     <t>Footprint</t>
   </si>
   <si>
-    <t>C1,C2,C24,C25,C26,</t>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>C1,C2,C24,C25,C26,C5,C12,C13,C30,</t>
   </si>
   <si>
     <t>100n</t>
@@ -50,16 +53,16 @@
     <t>Capacitor_SMD:C_1206_3216Metric</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/cl31b104kbcnnnc/kondensatory-mlcc-smd/samsung/</t>
+  </si>
+  <si>
     <t>C3,C4,C6,C7,C9,C21,C22,C23,</t>
   </si>
   <si>
     <t>22u</t>
   </si>
   <si>
-    <t>C5,C12,C13,C30,</t>
-  </si>
-  <si>
-    <t>0.1u</t>
+    <t>https://www.tme.eu/pl/details/grm31cr61e226ke15l/kondensatory-mlcc-smd/murata/</t>
   </si>
   <si>
     <t>C8,C10,C11,C14,C15,C16,C17,C18,C19,C20,</t>
@@ -68,24 +71,36 @@
     <t>10u</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/cl31a106kahnnne/kondensatory-mlcc-smd/samsung/</t>
+  </si>
+  <si>
     <t>C27,</t>
   </si>
   <si>
     <t>4.7u</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/cl31a475kahnnne/kondensatory-mlcc-smd/samsung/</t>
+  </si>
+  <si>
     <t>C28,</t>
   </si>
   <si>
     <t>1u</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/cl31b105kbhnnne/kondensatory-mlcc-smd/samsung/</t>
+  </si>
+  <si>
     <t>C29,</t>
   </si>
   <si>
     <t>10n</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/cc1206krx7r9bb103/kondensatory-mlcc-smd/yageo/</t>
+  </si>
+  <si>
     <t>D1,D2,</t>
   </si>
   <si>
@@ -95,6 +110,9 @@
     <t>LED_SMD:LED_1206_3216Metric_Pad1.42x1.75mm_HandSolder</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/of-smd3216r/diody-led-smd-kolorowe/optoflash/</t>
+  </si>
+  <si>
     <t>D3,D4,</t>
   </si>
   <si>
@@ -104,6 +122,9 @@
     <t>Diode_SMD:D_SMA</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/ss32bf-dc/diody-schottky-smd/dc-components/ss32bf/</t>
+  </si>
+  <si>
     <t>IC1,IC2,</t>
   </si>
   <si>
@@ -113,6 +134,9 @@
     <t>KiCad:TPS630701RNMR</t>
   </si>
   <si>
+    <t>https://www.mouser.pl/pl/ProductDetail/Texas-Instruments/TPS630701RNMR?qs=LuYMPh7GGMTyE4ON9PhzXw%3D%3D&amp;utm_id=22436684815&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=22426729329&amp;gbraid=0AAAAADn_wf3XMHQ6zRhB7voaiurS8BXmv&amp;gclid=CjwKCAjwn67VBhBnEiwAXUIN1THLO1qN-YgxaSPJNR99Heb35tPZ9mEgLFExLuTE6wJ6alpddn_etxoCz_UQAvD_BwE</t>
+  </si>
+  <si>
     <t>J1,</t>
   </si>
   <si>
@@ -122,6 +146,9 @@
     <t>Connector_USB:USB_C_Receptacle_GCT_USB4125-xx-x-0190_6P_TopMnt_Horizontal</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/usb4125-gf-a-0190/zlacza-usb-i-ieee1394/gct/</t>
+  </si>
+  <si>
     <t>J2,</t>
   </si>
   <si>
@@ -131,6 +158,9 @@
     <t>Connector_USB:USB_A_Molex_67643_Horizontal</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/mx-67643-0910/zlacza-usb-i-ieee1394/molex/67643-0910/</t>
+  </si>
+  <si>
     <t>L1,L2,</t>
   </si>
   <si>
@@ -140,6 +170,9 @@
     <t>Inductor_SMD:L_Coilcraft_XAL4020-XXX</t>
   </si>
   <si>
+    <t>https://www.coilcraft.com/en-us/products/power/shielded-inductors/molded-inductor/xfl/xfl4020/?skuId=2392|3785</t>
+  </si>
+  <si>
     <t>L3,</t>
   </si>
   <si>
@@ -149,6 +182,9 @@
     <t>Inductor_SMD:L_Coilcraft_XAL5030-XXX</t>
   </si>
   <si>
+    <t>https://www.coilcraft.com/en-us/products/power/shielded-inductors/molded-inductor/xfl/xfl4020/xfl4020-102/</t>
+  </si>
+  <si>
     <t>Q1,Q3,Q4,Q5,</t>
   </si>
   <si>
@@ -158,6 +194,9 @@
     <t>Package_TO_SOT_SMD:SOT-23</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/katalog/?queryPhrase=DMP3099L</t>
+  </si>
+  <si>
     <t>Q2,</t>
   </si>
   <si>
@@ -167,12 +206,18 @@
     <t>Package_SO:TSSOP-8_4.4x3mm_P0.65mm</t>
   </si>
   <si>
+    <t>https://pl.aliexpress.com/item/1005006168808626.html</t>
+  </si>
+  <si>
     <t>Q6,</t>
   </si>
   <si>
     <t>DMP3099L</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/dmp3099l-7/tranzystory-z-kanalem-p-smd/diodes-incorporated/</t>
+  </si>
+  <si>
     <t>R1,R2,R17,</t>
   </si>
   <si>
@@ -182,12 +227,18 @@
     <t>Resistor_SMD:R_1206_3216Metric</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/smd1206-1k-1%25/rezystory-smd/royalohm/1206s4f1001t5e/</t>
+  </si>
+  <si>
     <t>R3,</t>
   </si>
   <si>
     <t>680k</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/smd1206-680k-1%25/rezystory-smd/royalohm/1206s4f6803t5e/</t>
+  </si>
+  <si>
     <t>R4,</t>
   </si>
   <si>
@@ -275,81 +326,6 @@
     <t>0.05</t>
   </si>
   <si>
-    <t>TP1,</t>
-  </si>
-  <si>
-    <t>Bat-</t>
-  </si>
-  <si>
-    <t>TestPoint:TestPoint_Pad_D2.0mm</t>
-  </si>
-  <si>
-    <t>TP2,</t>
-  </si>
-  <si>
-    <t>Vbat</t>
-  </si>
-  <si>
-    <t>TP3,</t>
-  </si>
-  <si>
-    <t>Green_LED</t>
-  </si>
-  <si>
-    <t>TP4,</t>
-  </si>
-  <si>
-    <t>Panel_power</t>
-  </si>
-  <si>
-    <t>TP5,</t>
-  </si>
-  <si>
-    <t>Panel_gnd</t>
-  </si>
-  <si>
-    <t>TP6,</t>
-  </si>
-  <si>
-    <t>Leds_common_GND</t>
-  </si>
-  <si>
-    <t>TP7,</t>
-  </si>
-  <si>
-    <t>User_button-</t>
-  </si>
-  <si>
-    <t>TP8,</t>
-  </si>
-  <si>
-    <t>SWDIO</t>
-  </si>
-  <si>
-    <t>TP9,</t>
-  </si>
-  <si>
-    <t>SWCLK</t>
-  </si>
-  <si>
-    <t>TP10,</t>
-  </si>
-  <si>
-    <t>Red_LED</t>
-  </si>
-  <si>
-    <t>TP11,</t>
-  </si>
-  <si>
-    <t>Yellow_LED</t>
-  </si>
-  <si>
-    <t>TP12,</t>
-  </si>
-  <si>
-    <t>User_button+</t>
-  </si>
-  <si>
     <t>U1,</t>
   </si>
   <si>
@@ -359,6 +335,9 @@
     <t>Package_SO:SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.41x3.3mm_ThermalVias</t>
   </si>
   <si>
+    <t>https://allegro.pl/produkt/tp4056-4056-4056e-sop-8-5v-1a-battery-charge-controller-9f4e096b-2b10-4130-90a1-40e4469a7fbb?srsltid=AU7gw4Ug5GurgS5XfZw-PfUo3ehQAbW7DX0nK7h3GAm83NJ24pcqBrzw&amp;offerId=17285593534</t>
+  </si>
+  <si>
     <t>U2,</t>
   </si>
   <si>
@@ -368,6 +347,9 @@
     <t>Package_TO_SOT_SMD:SOT-363_SC-70-6</t>
   </si>
   <si>
+    <t>https://www.mouser.pl/pl/ProductDetail/Microchip-Technology/MCP4018T-103E-LTY?qs=savM97goi5hGuILh2wIQ1w%3D%3D</t>
+  </si>
+  <si>
     <t>U3,</t>
   </si>
   <si>
@@ -386,6 +368,9 @@
     <t>Package_DFN_QFN:Texas_RWU0007A_VQFN-7_2x2mm_P0.5mm</t>
   </si>
   <si>
+    <t>https://www.mouser.pl/pl/ProductDetail/Texas-Instruments/TPS61022RWUT?qs=vLWxofP3U2xU7G%2FuAQNIxA%3D%3D</t>
+  </si>
+  <si>
     <t>U5,</t>
   </si>
   <si>
@@ -395,6 +380,9 @@
     <t>Package_SO:TSSOP-20_4.4x6.5mm_P0.65mm</t>
   </si>
   <si>
+    <t>https://www.tme.eu/pl/details/stm32u031f8p6/mikrokontrolery-st/stmicroelectronics/</t>
+  </si>
+  <si>
     <t>U6,</t>
   </si>
   <si>
@@ -402,6 +390,9 @@
   </si>
   <si>
     <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/pl/details/ina219aidr/wzmacniacze-operacyjne-smd/texas-instruments/</t>
   </si>
 </sst>
 </file>
@@ -424,7 +415,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="20"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -575,12 +566,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -907,7 +904,7 @@
     <xf numFmtId="26" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -931,16 +928,16 @@
     <xf numFmtId="26" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -949,89 +946,89 @@
     <xf numFmtId="26" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="26" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="26" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1040,6 +1037,15 @@
     </xf>
     <xf numFmtId="26" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1574,16 +1580,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="41.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="6.85714285714286" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.4285714285714" style="1" customWidth="1"/>
     <col min="4" max="4" width="83.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="255.714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:4">
+    <row r="1" ht="26.25" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1596,736 +1603,640 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="1">
         <v>2</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="1">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="1">
         <v>2</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="C29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="1">
         <v>3</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="C33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1">
-        <v>100</v>
-      </c>
-      <c r="D29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="1">
-        <v>3</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>112</v>
+      </c>
+      <c r="E38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>116</v>
+      </c>
+      <c r="E39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>103</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>105</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>110</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="1">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E40" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>122</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" t="s">
-        <v>124</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://www.tme.eu/pl/details/cl31b104kbcnnnc/kondensatory-mlcc-smd/samsung/"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.tme.eu/pl/details/grm31cr61e226ke15l/kondensatory-mlcc-smd/murata/"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.tme.eu/pl/details/cl31a106kahnnne/kondensatory-mlcc-smd/samsung/"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://www.tme.eu/pl/details/cl31a475kahnnne/kondensatory-mlcc-smd/samsung/"/>
+    <hyperlink ref="E9" r:id="rId5" display="https://www.tme.eu/pl/details/ss32bf-dc/diody-schottky-smd/dc-components/ss32bf/"/>
+    <hyperlink ref="E8" r:id="rId6" display="https://www.tme.eu/pl/details/of-smd3216r/diody-led-smd-kolorowe/optoflash/"/>
+    <hyperlink ref="E17" r:id="rId7" display="https://www.tme.eu/pl/details/dmp3099l-7/tranzystory-z-kanalem-p-smd/diodes-incorporated/"/>
+    <hyperlink ref="E15" r:id="rId8" display="https://www.tme.eu/pl/katalog/?queryPhrase=DMP3099L"/>
+    <hyperlink ref="E36" r:id="rId9" display="https://www.mouser.pl/pl/ProductDetail/Microchip-Technology/MCP4018T-103E-LTY?qs=savM97goi5hGuILh2wIQ1w%3D%3D"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
